--- a/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250414.xlsx
+++ b/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250414.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25831"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usaf-my.dps.mil/personal/jennifer_shelton_4_us_af_mil/Documents/Desktop/Barge Status/Weeklyscorecard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional\04_Git\AI_Power_Studio\20250426_Vipers\01_source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="11_8B35F6202D1233D1E0FA8973B5BE447A6548BCBF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0D1DFB5-8C06-400A-993E-8F4BA53A4B51}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74649DCE-EC4F-4F4D-B8BA-885B952F1E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="10160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4670" yWindow="430" windowWidth="31320" windowHeight="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
   <si>
     <r>
       <rPr>
@@ -432,9 +432,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/dd/yyyy;@"/>
+    <numFmt numFmtId="176" formatCode="m/dd/yyyy;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -503,6 +503,12 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -705,19 +711,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="59">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" indent="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -729,31 +735,28 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -768,25 +771,100 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -807,84 +885,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -904,9 +910,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -944,9 +950,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -979,9 +985,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1014,9 +1037,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1193,6 +1233,7 @@
   <dimension ref="A1:X22"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="16.19921875" customWidth="1"/>
     <col min="3" max="3" width="6.8984375" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
@@ -1215,58 +1256,58 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="42"/>
+      <c r="C1" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="33"/>
     </row>
     <row r="2" spans="1:24" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4">
         <v>45761</v>
       </c>
-      <c r="C2" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46" t="s">
+      <c r="C2" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="47"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="50" t="s">
+      <c r="H2" s="38"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="51"/>
+      <c r="L2" s="42"/>
       <c r="M2" s="5"/>
-      <c r="N2" s="52" t="s">
+      <c r="N2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="54"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="6" t="s">
         <v>6</v>
       </c>
@@ -1422,40 +1463,40 @@
       <c r="X4" s="12"/>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="56"/>
-      <c r="C5" s="28" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="30"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="54"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="31" t="s">
+      <c r="K5" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="32"/>
-      <c r="S5" s="32"/>
-      <c r="T5" s="32"/>
-      <c r="U5" s="32"/>
-      <c r="V5" s="32"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="33"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="56"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="57"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23"/>
-      <c r="B6" s="58" t="s">
+      <c r="A6" s="22"/>
+      <c r="B6" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="24">
         <v>98</v>
       </c>
       <c r="D6" s="11">
@@ -1487,7 +1528,7 @@
       <c r="N6" s="11">
         <v>3995</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="14">
         <v>53</v>
       </c>
       <c r="P6" s="11">
@@ -1499,10 +1540,10 @@
       <c r="R6" s="11">
         <v>9</v>
       </c>
-      <c r="S6" s="15">
+      <c r="S6" s="14">
         <v>11</v>
       </c>
-      <c r="T6" s="15">
+      <c r="T6" s="14">
         <v>11</v>
       </c>
       <c r="U6" s="13">
@@ -1515,366 +1556,378 @@
       <c r="X6" s="12"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="57" t="s">
+      <c r="A7" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="15">
         <v>6</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="16">
+      <c r="E7" s="15">
         <v>12</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="15">
         <v>10</v>
       </c>
       <c r="G7" s="12"/>
-      <c r="H7" s="16">
+      <c r="H7" s="15">
         <v>8</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>9</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="12"/>
-      <c r="L7" s="16">
+      <c r="L7" s="15">
         <v>8</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="15">
         <v>8</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="15">
         <v>771</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="16">
         <v>6</v>
       </c>
-      <c r="P7" s="16">
+      <c r="P7" s="15">
         <v>12</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="15">
         <v>9</v>
       </c>
       <c r="R7" s="12"/>
-      <c r="S7" s="17">
-        <v>1</v>
-      </c>
-      <c r="T7" s="17">
-        <v>1</v>
-      </c>
-      <c r="U7" s="18">
-        <v>1</v>
-      </c>
-      <c r="V7" s="17">
+      <c r="S7" s="16">
+        <v>1</v>
+      </c>
+      <c r="T7" s="16">
+        <v>1</v>
+      </c>
+      <c r="U7" s="17">
+        <v>1</v>
+      </c>
+      <c r="V7" s="16">
         <v>3</v>
       </c>
       <c r="W7" s="12"/>
       <c r="X7" s="12"/>
     </row>
     <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35"/>
-      <c r="B8" s="22" t="s">
+      <c r="A8" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="15">
         <v>10</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <v>12</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>9</v>
       </c>
       <c r="G8" s="12"/>
-      <c r="H8" s="16">
-        <v>2</v>
-      </c>
-      <c r="I8" s="16">
+      <c r="H8" s="15">
+        <v>2</v>
+      </c>
+      <c r="I8" s="15">
         <v>4</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K8" s="12"/>
-      <c r="L8" s="16">
-        <v>1</v>
-      </c>
-      <c r="M8" s="16">
+      <c r="L8" s="15">
+        <v>1</v>
+      </c>
+      <c r="M8" s="15">
         <v>3</v>
       </c>
-      <c r="N8" s="16">
+      <c r="N8" s="15">
         <v>770</v>
       </c>
-      <c r="O8" s="18">
+      <c r="O8" s="17">
         <v>10</v>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="15">
         <v>12</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="15">
         <v>8</v>
       </c>
-      <c r="R8" s="16">
-        <v>2</v>
-      </c>
-      <c r="S8" s="18">
-        <v>2</v>
-      </c>
-      <c r="T8" s="17">
-        <v>1</v>
-      </c>
-      <c r="U8" s="18">
-        <v>2</v>
-      </c>
-      <c r="V8" s="18">
+      <c r="R8" s="15">
+        <v>2</v>
+      </c>
+      <c r="S8" s="17">
+        <v>2</v>
+      </c>
+      <c r="T8" s="16">
+        <v>1</v>
+      </c>
+      <c r="U8" s="17">
+        <v>2</v>
+      </c>
+      <c r="V8" s="17">
         <v>3</v>
       </c>
       <c r="W8" s="12"/>
       <c r="X8" s="12"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
-      <c r="B9" s="22" t="s">
+      <c r="A9" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="15">
         <v>20</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <v>20</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>18</v>
       </c>
       <c r="G9" s="12"/>
-      <c r="H9" s="16">
+      <c r="H9" s="15">
         <v>10</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="15">
         <v>11</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K9" s="12"/>
-      <c r="L9" s="16">
+      <c r="L9" s="15">
         <v>10</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="15">
         <v>10</v>
       </c>
-      <c r="N9" s="16">
+      <c r="N9" s="15">
         <v>1368</v>
       </c>
-      <c r="O9" s="18">
+      <c r="O9" s="17">
         <v>20</v>
       </c>
-      <c r="P9" s="16">
+      <c r="P9" s="15">
         <v>20</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9" s="15">
         <v>18</v>
       </c>
-      <c r="R9" s="16">
+      <c r="R9" s="15">
         <v>5</v>
       </c>
-      <c r="S9" s="18">
+      <c r="S9" s="17">
         <v>6</v>
       </c>
-      <c r="T9" s="18">
+      <c r="T9" s="17">
         <v>6</v>
       </c>
-      <c r="U9" s="17">
+      <c r="U9" s="16">
         <v>3</v>
       </c>
-      <c r="V9" s="19"/>
+      <c r="V9" s="18"/>
       <c r="W9" s="12"/>
       <c r="X9" s="12"/>
     </row>
     <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="35"/>
-      <c r="B10" s="22" t="s">
+      <c r="A10" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="15">
         <v>2</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="16">
+      <c r="E10" s="15">
         <v>4</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>11</v>
       </c>
       <c r="G10" s="12"/>
-      <c r="H10" s="16">
-        <v>2</v>
-      </c>
-      <c r="I10" s="16">
+      <c r="H10" s="15">
+        <v>2</v>
+      </c>
+      <c r="I10" s="15">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K10" s="12"/>
-      <c r="L10" s="16">
-        <v>2</v>
-      </c>
-      <c r="M10" s="16">
-        <v>1</v>
-      </c>
-      <c r="N10" s="16">
+      <c r="L10" s="15">
+        <v>2</v>
+      </c>
+      <c r="M10" s="15">
+        <v>1</v>
+      </c>
+      <c r="N10" s="15">
         <v>128</v>
       </c>
-      <c r="O10" s="19"/>
-      <c r="P10" s="16">
+      <c r="O10" s="18"/>
+      <c r="P10" s="15">
         <v>3</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="15">
         <v>7</v>
       </c>
       <c r="R10" s="12"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="20"/>
-      <c r="V10" s="19"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="18"/>
       <c r="W10" s="12"/>
       <c r="X10" s="12"/>
     </row>
     <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="35"/>
-      <c r="B11" s="22" t="s">
+      <c r="A11" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="15">
         <v>52</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>13</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>7</v>
       </c>
       <c r="G11" s="12"/>
-      <c r="H11" s="16">
+      <c r="H11" s="15">
         <v>4</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="15">
         <v>12</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K11" s="12"/>
-      <c r="L11" s="16">
-        <v>2</v>
-      </c>
-      <c r="M11" s="16">
+      <c r="L11" s="15">
+        <v>2</v>
+      </c>
+      <c r="M11" s="15">
         <v>8</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="15">
         <v>506</v>
       </c>
-      <c r="O11" s="18">
+      <c r="O11" s="17">
         <v>9</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="15">
         <v>13</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="15">
         <v>6</v>
       </c>
-      <c r="R11" s="16">
-        <v>1</v>
-      </c>
-      <c r="S11" s="17">
-        <v>1</v>
-      </c>
-      <c r="T11" s="18">
-        <v>1</v>
-      </c>
-      <c r="U11" s="18">
+      <c r="R11" s="15">
+        <v>1</v>
+      </c>
+      <c r="S11" s="16">
+        <v>1</v>
+      </c>
+      <c r="T11" s="17">
+        <v>1</v>
+      </c>
+      <c r="U11" s="17">
         <v>4</v>
       </c>
-      <c r="V11" s="18">
+      <c r="V11" s="17">
         <v>2</v>
       </c>
       <c r="W11" s="12"/>
       <c r="X11" s="12"/>
     </row>
     <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="35"/>
-      <c r="B12" s="22" t="s">
+      <c r="A12" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="15">
         <v>8</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <v>15</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>12</v>
       </c>
       <c r="G12" s="12"/>
-      <c r="H12" s="16">
+      <c r="H12" s="15">
         <v>5</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="15">
         <v>4</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K12" s="12"/>
-      <c r="L12" s="16">
+      <c r="L12" s="15">
         <v>4</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="15">
         <v>4</v>
       </c>
-      <c r="N12" s="16">
+      <c r="N12" s="15">
         <v>450</v>
       </c>
-      <c r="O12" s="18">
+      <c r="O12" s="17">
         <v>8</v>
       </c>
-      <c r="P12" s="16">
+      <c r="P12" s="15">
         <v>15</v>
       </c>
-      <c r="Q12" s="16">
+      <c r="Q12" s="15">
         <v>12</v>
       </c>
-      <c r="R12" s="16">
-        <v>1</v>
-      </c>
-      <c r="S12" s="17">
-        <v>1</v>
-      </c>
-      <c r="T12" s="18">
-        <v>2</v>
-      </c>
-      <c r="U12" s="17">
-        <v>1</v>
-      </c>
-      <c r="V12" s="18">
+      <c r="R12" s="15">
+        <v>1</v>
+      </c>
+      <c r="S12" s="16">
+        <v>1</v>
+      </c>
+      <c r="T12" s="17">
+        <v>2</v>
+      </c>
+      <c r="U12" s="16">
+        <v>1</v>
+      </c>
+      <c r="V12" s="17">
         <v>3</v>
       </c>
       <c r="W12" s="12"/>
       <c r="X12" s="12"/>
     </row>
     <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="22" t="s">
+      <c r="A13" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="12"/>
@@ -1890,51 +1943,51 @@
       <c r="K13" s="12"/>
       <c r="L13" s="12"/>
       <c r="M13" s="12"/>
-      <c r="N13" s="16">
-        <v>2</v>
-      </c>
-      <c r="O13" s="20"/>
+      <c r="N13" s="15">
+        <v>2</v>
+      </c>
+      <c r="O13" s="19"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="20"/>
-      <c r="V13" s="20"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
       <c r="W13" s="12"/>
       <c r="X13" s="12"/>
     </row>
     <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="12"/>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="54"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="31" t="s">
+      <c r="K14" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
-      <c r="O14" s="32"/>
-      <c r="P14" s="32"/>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="32"/>
-      <c r="S14" s="32"/>
-      <c r="T14" s="32"/>
-      <c r="U14" s="32"/>
-      <c r="V14" s="32"/>
-      <c r="W14" s="32"/>
-      <c r="X14" s="33"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="56"/>
+      <c r="N14" s="56"/>
+      <c r="O14" s="56"/>
+      <c r="P14" s="56"/>
+      <c r="Q14" s="56"/>
+      <c r="R14" s="56"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="56"/>
+      <c r="U14" s="56"/>
+      <c r="V14" s="56"/>
+      <c r="W14" s="56"/>
+      <c r="X14" s="57"/>
     </row>
     <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="58" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="11">
@@ -1992,220 +2045,226 @@
       <c r="U15" s="13">
         <v>27</v>
       </c>
-      <c r="V15" s="15">
+      <c r="V15" s="14">
         <v>11</v>
       </c>
       <c r="W15" s="12"/>
       <c r="X15" s="12"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="15">
         <v>22</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="16">
+      <c r="E16" s="15">
         <v>18</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>8</v>
       </c>
       <c r="G16" s="12"/>
-      <c r="H16" s="16">
+      <c r="H16" s="15">
         <v>10</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="15">
         <v>7</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K16" s="12"/>
-      <c r="L16" s="16">
+      <c r="L16" s="15">
         <v>10</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="15">
         <v>6</v>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="15">
         <v>1063</v>
       </c>
-      <c r="O16" s="18">
+      <c r="O16" s="17">
         <v>22</v>
       </c>
-      <c r="P16" s="16">
+      <c r="P16" s="15">
         <v>18</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="15">
         <v>8</v>
       </c>
-      <c r="R16" s="16">
+      <c r="R16" s="15">
         <v>6</v>
       </c>
-      <c r="S16" s="18">
+      <c r="S16" s="17">
         <v>4</v>
       </c>
-      <c r="T16" s="17">
+      <c r="T16" s="16">
         <v>3</v>
       </c>
-      <c r="U16" s="18">
+      <c r="U16" s="17">
         <v>6</v>
       </c>
-      <c r="V16" s="17">
+      <c r="V16" s="16">
         <v>3</v>
       </c>
       <c r="W16" s="12"/>
       <c r="X16" s="12"/>
     </row>
     <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="22" t="s">
+      <c r="A17" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="15">
         <v>11</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="16">
+      <c r="E17" s="15">
         <v>16</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="15">
         <v>23</v>
       </c>
-      <c r="G17" s="16">
-        <v>1</v>
-      </c>
-      <c r="H17" s="16">
-        <v>2</v>
-      </c>
-      <c r="I17" s="16">
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="15">
+        <v>2</v>
+      </c>
+      <c r="I17" s="15">
         <v>5</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K17" s="12"/>
-      <c r="L17" s="16">
-        <v>1</v>
-      </c>
-      <c r="M17" s="16">
+      <c r="L17" s="15">
+        <v>1</v>
+      </c>
+      <c r="M17" s="15">
         <v>3</v>
       </c>
-      <c r="N17" s="16">
+      <c r="N17" s="15">
         <v>851</v>
       </c>
-      <c r="O17" s="18">
+      <c r="O17" s="17">
         <v>11</v>
       </c>
-      <c r="P17" s="16">
+      <c r="P17" s="15">
         <v>15</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="Q17" s="15">
         <v>22</v>
       </c>
-      <c r="R17" s="16">
-        <v>2</v>
-      </c>
-      <c r="S17" s="18">
+      <c r="R17" s="15">
+        <v>2</v>
+      </c>
+      <c r="S17" s="17">
         <v>3</v>
       </c>
-      <c r="T17" s="18">
-        <v>2</v>
-      </c>
-      <c r="U17" s="17">
-        <v>1</v>
-      </c>
-      <c r="V17" s="18">
+      <c r="T17" s="17">
+        <v>2</v>
+      </c>
+      <c r="U17" s="16">
+        <v>1</v>
+      </c>
+      <c r="V17" s="17">
         <v>3</v>
       </c>
       <c r="W17" s="12"/>
       <c r="X17" s="12"/>
     </row>
     <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="22" t="s">
+      <c r="A18" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="15">
         <v>30</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="16">
+      <c r="E18" s="15">
         <v>30</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>15</v>
       </c>
       <c r="G18" s="12"/>
-      <c r="H18" s="16">
+      <c r="H18" s="15">
         <v>11</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="15">
         <v>4</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K18" s="12"/>
-      <c r="L18" s="16">
+      <c r="L18" s="15">
         <v>11</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="15">
         <v>4</v>
       </c>
-      <c r="N18" s="16">
+      <c r="N18" s="15">
         <v>1857</v>
       </c>
-      <c r="O18" s="18">
+      <c r="O18" s="17">
         <v>30</v>
       </c>
-      <c r="P18" s="16">
+      <c r="P18" s="15">
         <v>30</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="Q18" s="15">
         <v>15</v>
       </c>
-      <c r="R18" s="16">
+      <c r="R18" s="15">
         <v>6</v>
       </c>
-      <c r="S18" s="18">
+      <c r="S18" s="17">
         <v>5</v>
       </c>
-      <c r="T18" s="18">
+      <c r="T18" s="17">
         <v>5</v>
       </c>
-      <c r="U18" s="18">
+      <c r="U18" s="17">
         <v>10</v>
       </c>
-      <c r="V18" s="18">
+      <c r="V18" s="17">
         <v>4</v>
       </c>
       <c r="W18" s="12"/>
       <c r="X18" s="12"/>
     </row>
     <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="22" t="s">
+      <c r="A19" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="15">
         <v>10</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="16">
+      <c r="E19" s="15">
         <v>3</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="15">
         <v>10</v>
       </c>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
-      <c r="I19" s="16">
+      <c r="I19" s="15">
         <v>2</v>
       </c>
       <c r="J19" s="2" t="s">
@@ -2213,160 +2272,166 @@
       </c>
       <c r="K19" s="12"/>
       <c r="L19" s="12"/>
-      <c r="M19" s="16">
-        <v>2</v>
-      </c>
-      <c r="N19" s="16">
+      <c r="M19" s="15">
+        <v>2</v>
+      </c>
+      <c r="N19" s="15">
         <v>291</v>
       </c>
-      <c r="O19" s="18">
+      <c r="O19" s="17">
         <v>10</v>
       </c>
-      <c r="P19" s="16">
+      <c r="P19" s="15">
         <v>3</v>
       </c>
-      <c r="Q19" s="16">
+      <c r="Q19" s="15">
         <v>9</v>
       </c>
-      <c r="R19" s="16">
-        <v>2</v>
-      </c>
-      <c r="S19" s="18">
+      <c r="R19" s="15">
+        <v>2</v>
+      </c>
+      <c r="S19" s="17">
         <v>4</v>
       </c>
-      <c r="T19" s="18">
-        <v>2</v>
-      </c>
-      <c r="U19" s="18">
-        <v>1</v>
-      </c>
-      <c r="V19" s="18">
+      <c r="T19" s="17">
+        <v>2</v>
+      </c>
+      <c r="U19" s="17">
+        <v>1</v>
+      </c>
+      <c r="V19" s="17">
         <v>1</v>
       </c>
       <c r="W19" s="12"/>
       <c r="X19" s="12"/>
     </row>
     <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="22" t="s">
+      <c r="A20" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="15">
         <v>7</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <v>18</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>17</v>
       </c>
       <c r="G20" s="12"/>
-      <c r="H20" s="16">
+      <c r="H20" s="15">
         <v>5</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="15">
         <v>10</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K20" s="12"/>
-      <c r="L20" s="16">
-        <v>2</v>
-      </c>
-      <c r="M20" s="16">
+      <c r="L20" s="15">
+        <v>2</v>
+      </c>
+      <c r="M20" s="15">
         <v>7</v>
       </c>
-      <c r="N20" s="16">
+      <c r="N20" s="15">
         <v>782</v>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="16">
         <v>6</v>
       </c>
-      <c r="P20" s="16">
+      <c r="P20" s="15">
         <v>18</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="Q20" s="15">
         <v>17</v>
       </c>
       <c r="R20" s="12"/>
-      <c r="S20" s="17">
-        <v>1</v>
-      </c>
-      <c r="T20" s="17">
-        <v>2</v>
-      </c>
-      <c r="U20" s="18">
+      <c r="S20" s="16">
+        <v>1</v>
+      </c>
+      <c r="T20" s="16">
+        <v>2</v>
+      </c>
+      <c r="U20" s="17">
         <v>3</v>
       </c>
-      <c r="V20" s="19"/>
+      <c r="V20" s="18"/>
       <c r="W20" s="12"/>
       <c r="X20" s="12"/>
     </row>
     <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="22" t="s">
+      <c r="A21" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="15">
         <v>13</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="16">
+      <c r="E21" s="15">
         <v>7</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="15">
         <v>9</v>
       </c>
       <c r="G21" s="12"/>
-      <c r="H21" s="16">
-        <v>1</v>
-      </c>
-      <c r="I21" s="16">
+      <c r="H21" s="15">
+        <v>1</v>
+      </c>
+      <c r="I21" s="15">
         <v>3</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K21" s="12"/>
-      <c r="L21" s="16">
-        <v>1</v>
-      </c>
-      <c r="M21" s="16">
+      <c r="L21" s="15">
+        <v>1</v>
+      </c>
+      <c r="M21" s="15">
         <v>3</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="15">
         <v>467</v>
       </c>
-      <c r="O21" s="18">
+      <c r="O21" s="17">
         <v>13</v>
       </c>
-      <c r="P21" s="16">
+      <c r="P21" s="15">
         <v>7</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="Q21" s="15">
         <v>9</v>
       </c>
-      <c r="R21" s="16">
-        <v>2</v>
-      </c>
-      <c r="S21" s="18">
-        <v>2</v>
-      </c>
-      <c r="T21" s="18">
+      <c r="R21" s="15">
+        <v>2</v>
+      </c>
+      <c r="S21" s="17">
+        <v>2</v>
+      </c>
+      <c r="T21" s="17">
         <v>3</v>
       </c>
-      <c r="U21" s="18">
+      <c r="U21" s="17">
         <v>6</v>
       </c>
-      <c r="V21" s="19"/>
+      <c r="V21" s="18"/>
       <c r="W21" s="12"/>
       <c r="X21" s="12"/>
     </row>
     <row r="22" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27"/>
-      <c r="B22" s="22" t="s">
+      <c r="A22" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C22" s="12"/>
@@ -2382,22 +2447,26 @@
       <c r="K22" s="12"/>
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
-      <c r="N22" s="16">
-        <v>1</v>
-      </c>
-      <c r="O22" s="20"/>
+      <c r="N22" s="15">
+        <v>1</v>
+      </c>
+      <c r="O22" s="19"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
       <c r="R22" s="12"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="20"/>
-      <c r="U22" s="20"/>
-      <c r="V22" s="20"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="19"/>
+      <c r="U22" s="19"/>
+      <c r="V22" s="19"/>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="11">
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="K14:X14"/>
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="R1:X1"/>
     <mergeCell ref="C2:F2"/>
@@ -2405,13 +2474,8 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="A16:A22"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="K14:X14"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2444,58 +2508,58 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="42"/>
+      <c r="C1" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="33"/>
     </row>
     <row r="2" spans="1:24" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4">
         <v>45761</v>
       </c>
-      <c r="C2" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46" t="s">
+      <c r="C2" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="47"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="50" t="s">
+      <c r="H2" s="38"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="51"/>
+      <c r="L2" s="42"/>
       <c r="M2" s="5"/>
-      <c r="N2" s="52" t="s">
+      <c r="N2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="54"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="6" t="s">
         <v>6</v>
       </c>
@@ -2652,38 +2716,38 @@
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12"/>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="30"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="54"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="31" t="s">
+      <c r="K5" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="32"/>
-      <c r="S5" s="32"/>
-      <c r="T5" s="32"/>
-      <c r="U5" s="32"/>
-      <c r="V5" s="32"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="33"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="56"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="57"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>38</v>
       </c>
       <c r="C6" s="11">
@@ -2718,7 +2782,7 @@
       <c r="N6" s="11">
         <v>3995</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="14">
         <v>53</v>
       </c>
       <c r="P6" s="11">
@@ -2730,10 +2794,10 @@
       <c r="R6" s="11">
         <v>9</v>
       </c>
-      <c r="S6" s="15">
+      <c r="S6" s="14">
         <v>11</v>
       </c>
-      <c r="T6" s="15">
+      <c r="T6" s="14">
         <v>11</v>
       </c>
       <c r="U6" s="13">
@@ -2746,364 +2810,364 @@
       <c r="X6" s="12"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35"/>
-      <c r="B7" s="22" t="s">
+      <c r="A7" s="50"/>
+      <c r="B7" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="15">
         <v>6</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="16">
+      <c r="E7" s="15">
         <v>12</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="15">
         <v>10</v>
       </c>
       <c r="G7" s="12"/>
-      <c r="H7" s="16">
+      <c r="H7" s="15">
         <v>8</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>9</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="12"/>
-      <c r="L7" s="16">
+      <c r="L7" s="15">
         <v>8</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="15">
         <v>8</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="15">
         <v>771</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="16">
         <v>6</v>
       </c>
-      <c r="P7" s="16">
+      <c r="P7" s="15">
         <v>12</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="15">
         <v>9</v>
       </c>
       <c r="R7" s="12"/>
-      <c r="S7" s="17">
-        <v>1</v>
-      </c>
-      <c r="T7" s="17">
-        <v>1</v>
-      </c>
-      <c r="U7" s="18">
-        <v>1</v>
-      </c>
-      <c r="V7" s="17">
+      <c r="S7" s="16">
+        <v>1</v>
+      </c>
+      <c r="T7" s="16">
+        <v>1</v>
+      </c>
+      <c r="U7" s="17">
+        <v>1</v>
+      </c>
+      <c r="V7" s="16">
         <v>3</v>
       </c>
       <c r="W7" s="12"/>
       <c r="X7" s="12"/>
     </row>
     <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35"/>
-      <c r="B8" s="22" t="s">
+      <c r="A8" s="50"/>
+      <c r="B8" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="15">
         <v>10</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <v>12</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>9</v>
       </c>
       <c r="G8" s="12"/>
-      <c r="H8" s="16">
-        <v>2</v>
-      </c>
-      <c r="I8" s="16">
+      <c r="H8" s="15">
+        <v>2</v>
+      </c>
+      <c r="I8" s="15">
         <v>4</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K8" s="12"/>
-      <c r="L8" s="16">
-        <v>1</v>
-      </c>
-      <c r="M8" s="16">
+      <c r="L8" s="15">
+        <v>1</v>
+      </c>
+      <c r="M8" s="15">
         <v>3</v>
       </c>
-      <c r="N8" s="16">
+      <c r="N8" s="15">
         <v>770</v>
       </c>
-      <c r="O8" s="18">
+      <c r="O8" s="17">
         <v>10</v>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="15">
         <v>12</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="15">
         <v>8</v>
       </c>
-      <c r="R8" s="16">
-        <v>2</v>
-      </c>
-      <c r="S8" s="18">
-        <v>2</v>
-      </c>
-      <c r="T8" s="17">
-        <v>1</v>
-      </c>
-      <c r="U8" s="18">
-        <v>2</v>
-      </c>
-      <c r="V8" s="18">
+      <c r="R8" s="15">
+        <v>2</v>
+      </c>
+      <c r="S8" s="17">
+        <v>2</v>
+      </c>
+      <c r="T8" s="16">
+        <v>1</v>
+      </c>
+      <c r="U8" s="17">
+        <v>2</v>
+      </c>
+      <c r="V8" s="17">
         <v>3</v>
       </c>
       <c r="W8" s="12"/>
       <c r="X8" s="12"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
-      <c r="B9" s="22" t="s">
+      <c r="A9" s="50"/>
+      <c r="B9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="15">
         <v>20</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <v>20</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>18</v>
       </c>
       <c r="G9" s="12"/>
-      <c r="H9" s="16">
+      <c r="H9" s="15">
         <v>10</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="15">
         <v>11</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K9" s="12"/>
-      <c r="L9" s="16">
+      <c r="L9" s="15">
         <v>10</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="15">
         <v>10</v>
       </c>
-      <c r="N9" s="16">
+      <c r="N9" s="15">
         <v>1368</v>
       </c>
-      <c r="O9" s="18">
+      <c r="O9" s="17">
         <v>20</v>
       </c>
-      <c r="P9" s="16">
+      <c r="P9" s="15">
         <v>20</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9" s="15">
         <v>18</v>
       </c>
-      <c r="R9" s="16">
+      <c r="R9" s="15">
         <v>5</v>
       </c>
-      <c r="S9" s="18">
+      <c r="S9" s="17">
         <v>6</v>
       </c>
-      <c r="T9" s="18">
+      <c r="T9" s="17">
         <v>6</v>
       </c>
-      <c r="U9" s="17">
+      <c r="U9" s="16">
         <v>3</v>
       </c>
-      <c r="V9" s="19"/>
+      <c r="V9" s="18"/>
       <c r="W9" s="12"/>
       <c r="X9" s="12"/>
     </row>
     <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="35"/>
-      <c r="B10" s="22" t="s">
+      <c r="A10" s="50"/>
+      <c r="B10" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="15">
         <v>2</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="16">
+      <c r="E10" s="15">
         <v>4</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>11</v>
       </c>
       <c r="G10" s="12"/>
-      <c r="H10" s="16">
-        <v>2</v>
-      </c>
-      <c r="I10" s="16">
+      <c r="H10" s="15">
+        <v>2</v>
+      </c>
+      <c r="I10" s="15">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K10" s="12"/>
-      <c r="L10" s="16">
-        <v>2</v>
-      </c>
-      <c r="M10" s="16">
-        <v>1</v>
-      </c>
-      <c r="N10" s="16">
+      <c r="L10" s="15">
+        <v>2</v>
+      </c>
+      <c r="M10" s="15">
+        <v>1</v>
+      </c>
+      <c r="N10" s="15">
         <v>128</v>
       </c>
-      <c r="O10" s="19"/>
-      <c r="P10" s="16">
+      <c r="O10" s="18"/>
+      <c r="P10" s="15">
         <v>3</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="15">
         <v>7</v>
       </c>
       <c r="R10" s="12"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="20"/>
-      <c r="V10" s="19"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="18"/>
       <c r="W10" s="12"/>
       <c r="X10" s="12"/>
     </row>
     <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="35"/>
-      <c r="B11" s="22" t="s">
+      <c r="A11" s="50"/>
+      <c r="B11" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="15">
         <v>52</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>13</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>7</v>
       </c>
       <c r="G11" s="12"/>
-      <c r="H11" s="16">
+      <c r="H11" s="15">
         <v>4</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="15">
         <v>12</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K11" s="12"/>
-      <c r="L11" s="16">
-        <v>2</v>
-      </c>
-      <c r="M11" s="16">
+      <c r="L11" s="15">
+        <v>2</v>
+      </c>
+      <c r="M11" s="15">
         <v>8</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="15">
         <v>506</v>
       </c>
-      <c r="O11" s="18">
+      <c r="O11" s="17">
         <v>9</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="15">
         <v>13</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="15">
         <v>6</v>
       </c>
-      <c r="R11" s="16">
-        <v>1</v>
-      </c>
-      <c r="S11" s="17">
-        <v>1</v>
-      </c>
-      <c r="T11" s="18">
-        <v>1</v>
-      </c>
-      <c r="U11" s="18">
+      <c r="R11" s="15">
+        <v>1</v>
+      </c>
+      <c r="S11" s="16">
+        <v>1</v>
+      </c>
+      <c r="T11" s="17">
+        <v>1</v>
+      </c>
+      <c r="U11" s="17">
         <v>4</v>
       </c>
-      <c r="V11" s="18">
+      <c r="V11" s="17">
         <v>2</v>
       </c>
       <c r="W11" s="12"/>
       <c r="X11" s="12"/>
     </row>
     <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="35"/>
-      <c r="B12" s="22" t="s">
+      <c r="A12" s="50"/>
+      <c r="B12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="15">
         <v>8</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <v>15</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>12</v>
       </c>
       <c r="G12" s="12"/>
-      <c r="H12" s="16">
+      <c r="H12" s="15">
         <v>5</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="15">
         <v>4</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K12" s="12"/>
-      <c r="L12" s="16">
+      <c r="L12" s="15">
         <v>4</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="15">
         <v>4</v>
       </c>
-      <c r="N12" s="16">
+      <c r="N12" s="15">
         <v>450</v>
       </c>
-      <c r="O12" s="18">
+      <c r="O12" s="17">
         <v>8</v>
       </c>
-      <c r="P12" s="16">
+      <c r="P12" s="15">
         <v>15</v>
       </c>
-      <c r="Q12" s="16">
+      <c r="Q12" s="15">
         <v>12</v>
       </c>
-      <c r="R12" s="16">
-        <v>1</v>
-      </c>
-      <c r="S12" s="17">
-        <v>1</v>
-      </c>
-      <c r="T12" s="18">
-        <v>2</v>
-      </c>
-      <c r="U12" s="17">
-        <v>1</v>
-      </c>
-      <c r="V12" s="18">
+      <c r="R12" s="15">
+        <v>1</v>
+      </c>
+      <c r="S12" s="16">
+        <v>1</v>
+      </c>
+      <c r="T12" s="17">
+        <v>2</v>
+      </c>
+      <c r="U12" s="16">
+        <v>1</v>
+      </c>
+      <c r="V12" s="17">
         <v>3</v>
       </c>
       <c r="W12" s="12"/>
       <c r="X12" s="12"/>
     </row>
     <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="22" t="s">
+      <c r="A13" s="51"/>
+      <c r="B13" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="12"/>
@@ -3119,54 +3183,54 @@
       <c r="K13" s="12"/>
       <c r="L13" s="12"/>
       <c r="M13" s="12"/>
-      <c r="N13" s="16">
-        <v>2</v>
-      </c>
-      <c r="O13" s="20"/>
+      <c r="N13" s="15">
+        <v>2</v>
+      </c>
+      <c r="O13" s="19"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="20"/>
-      <c r="V13" s="20"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
       <c r="W13" s="12"/>
       <c r="X13" s="12"/>
     </row>
     <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="12"/>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="54"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="31" t="s">
+      <c r="K14" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
-      <c r="O14" s="32"/>
-      <c r="P14" s="32"/>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="32"/>
-      <c r="S14" s="32"/>
-      <c r="T14" s="32"/>
-      <c r="U14" s="32"/>
-      <c r="V14" s="32"/>
-      <c r="W14" s="32"/>
-      <c r="X14" s="33"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="56"/>
+      <c r="N14" s="56"/>
+      <c r="O14" s="56"/>
+      <c r="P14" s="56"/>
+      <c r="Q14" s="56"/>
+      <c r="R14" s="56"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="56"/>
+      <c r="U14" s="56"/>
+      <c r="V14" s="56"/>
+      <c r="W14" s="56"/>
+      <c r="X14" s="57"/>
     </row>
     <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="23" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="11">
@@ -3224,218 +3288,218 @@
       <c r="U15" s="13">
         <v>27</v>
       </c>
-      <c r="V15" s="15">
+      <c r="V15" s="14">
         <v>11</v>
       </c>
       <c r="W15" s="12"/>
       <c r="X15" s="12"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="47"/>
+      <c r="B16" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="15">
         <v>22</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="16">
+      <c r="E16" s="15">
         <v>18</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>8</v>
       </c>
       <c r="G16" s="12"/>
-      <c r="H16" s="16">
+      <c r="H16" s="15">
         <v>10</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="15">
         <v>7</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K16" s="12"/>
-      <c r="L16" s="16">
+      <c r="L16" s="15">
         <v>10</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="15">
         <v>6</v>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="15">
         <v>1063</v>
       </c>
-      <c r="O16" s="18">
+      <c r="O16" s="17">
         <v>22</v>
       </c>
-      <c r="P16" s="16">
+      <c r="P16" s="15">
         <v>18</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="15">
         <v>8</v>
       </c>
-      <c r="R16" s="16">
+      <c r="R16" s="15">
         <v>6</v>
       </c>
-      <c r="S16" s="18">
+      <c r="S16" s="17">
         <v>4</v>
       </c>
-      <c r="T16" s="17">
+      <c r="T16" s="16">
         <v>3</v>
       </c>
-      <c r="U16" s="18">
+      <c r="U16" s="17">
         <v>6</v>
       </c>
-      <c r="V16" s="17">
+      <c r="V16" s="16">
         <v>3</v>
       </c>
       <c r="W16" s="12"/>
       <c r="X16" s="12"/>
     </row>
     <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="22" t="s">
+      <c r="A17" s="47"/>
+      <c r="B17" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="15">
         <v>11</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="16">
+      <c r="E17" s="15">
         <v>16</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="15">
         <v>23</v>
       </c>
-      <c r="G17" s="16">
-        <v>1</v>
-      </c>
-      <c r="H17" s="16">
-        <v>2</v>
-      </c>
-      <c r="I17" s="16">
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="15">
+        <v>2</v>
+      </c>
+      <c r="I17" s="15">
         <v>5</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K17" s="12"/>
-      <c r="L17" s="16">
-        <v>1</v>
-      </c>
-      <c r="M17" s="16">
+      <c r="L17" s="15">
+        <v>1</v>
+      </c>
+      <c r="M17" s="15">
         <v>3</v>
       </c>
-      <c r="N17" s="16">
+      <c r="N17" s="15">
         <v>851</v>
       </c>
-      <c r="O17" s="18">
+      <c r="O17" s="17">
         <v>11</v>
       </c>
-      <c r="P17" s="16">
+      <c r="P17" s="15">
         <v>15</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="Q17" s="15">
         <v>22</v>
       </c>
-      <c r="R17" s="16">
-        <v>2</v>
-      </c>
-      <c r="S17" s="18">
+      <c r="R17" s="15">
+        <v>2</v>
+      </c>
+      <c r="S17" s="17">
         <v>3</v>
       </c>
-      <c r="T17" s="18">
-        <v>2</v>
-      </c>
-      <c r="U17" s="17">
-        <v>1</v>
-      </c>
-      <c r="V17" s="18">
+      <c r="T17" s="17">
+        <v>2</v>
+      </c>
+      <c r="U17" s="16">
+        <v>1</v>
+      </c>
+      <c r="V17" s="17">
         <v>3</v>
       </c>
       <c r="W17" s="12"/>
       <c r="X17" s="12"/>
     </row>
     <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="22" t="s">
+      <c r="A18" s="47"/>
+      <c r="B18" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="15">
         <v>30</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="16">
+      <c r="E18" s="15">
         <v>30</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>15</v>
       </c>
       <c r="G18" s="12"/>
-      <c r="H18" s="16">
+      <c r="H18" s="15">
         <v>11</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="15">
         <v>4</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K18" s="12"/>
-      <c r="L18" s="16">
+      <c r="L18" s="15">
         <v>11</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="15">
         <v>4</v>
       </c>
-      <c r="N18" s="16">
+      <c r="N18" s="15">
         <v>1857</v>
       </c>
-      <c r="O18" s="18">
+      <c r="O18" s="17">
         <v>30</v>
       </c>
-      <c r="P18" s="16">
+      <c r="P18" s="15">
         <v>30</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="Q18" s="15">
         <v>15</v>
       </c>
-      <c r="R18" s="16">
+      <c r="R18" s="15">
         <v>6</v>
       </c>
-      <c r="S18" s="18">
+      <c r="S18" s="17">
         <v>5</v>
       </c>
-      <c r="T18" s="18">
+      <c r="T18" s="17">
         <v>5</v>
       </c>
-      <c r="U18" s="18">
+      <c r="U18" s="17">
         <v>10</v>
       </c>
-      <c r="V18" s="18">
+      <c r="V18" s="17">
         <v>4</v>
       </c>
       <c r="W18" s="12"/>
       <c r="X18" s="12"/>
     </row>
     <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="22" t="s">
+      <c r="A19" s="47"/>
+      <c r="B19" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="15">
         <v>10</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="16">
+      <c r="E19" s="15">
         <v>3</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="15">
         <v>10</v>
       </c>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
-      <c r="I19" s="16">
+      <c r="I19" s="15">
         <v>2</v>
       </c>
       <c r="J19" s="2" t="s">
@@ -3443,160 +3507,160 @@
       </c>
       <c r="K19" s="12"/>
       <c r="L19" s="12"/>
-      <c r="M19" s="16">
-        <v>2</v>
-      </c>
-      <c r="N19" s="16">
+      <c r="M19" s="15">
+        <v>2</v>
+      </c>
+      <c r="N19" s="15">
         <v>291</v>
       </c>
-      <c r="O19" s="18">
+      <c r="O19" s="17">
         <v>10</v>
       </c>
-      <c r="P19" s="16">
+      <c r="P19" s="15">
         <v>3</v>
       </c>
-      <c r="Q19" s="16">
+      <c r="Q19" s="15">
         <v>9</v>
       </c>
-      <c r="R19" s="16">
-        <v>2</v>
-      </c>
-      <c r="S19" s="18">
+      <c r="R19" s="15">
+        <v>2</v>
+      </c>
+      <c r="S19" s="17">
         <v>4</v>
       </c>
-      <c r="T19" s="18">
-        <v>2</v>
-      </c>
-      <c r="U19" s="18">
-        <v>1</v>
-      </c>
-      <c r="V19" s="18">
+      <c r="T19" s="17">
+        <v>2</v>
+      </c>
+      <c r="U19" s="17">
+        <v>1</v>
+      </c>
+      <c r="V19" s="17">
         <v>1</v>
       </c>
       <c r="W19" s="12"/>
       <c r="X19" s="12"/>
     </row>
     <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="22" t="s">
+      <c r="A20" s="47"/>
+      <c r="B20" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="15">
         <v>7</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <v>18</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>17</v>
       </c>
       <c r="G20" s="12"/>
-      <c r="H20" s="16">
+      <c r="H20" s="15">
         <v>5</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="15">
         <v>10</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K20" s="12"/>
-      <c r="L20" s="16">
-        <v>2</v>
-      </c>
-      <c r="M20" s="16">
+      <c r="L20" s="15">
+        <v>2</v>
+      </c>
+      <c r="M20" s="15">
         <v>7</v>
       </c>
-      <c r="N20" s="16">
+      <c r="N20" s="15">
         <v>782</v>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="16">
         <v>6</v>
       </c>
-      <c r="P20" s="16">
+      <c r="P20" s="15">
         <v>18</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="Q20" s="15">
         <v>17</v>
       </c>
       <c r="R20" s="12"/>
-      <c r="S20" s="17">
-        <v>1</v>
-      </c>
-      <c r="T20" s="17">
-        <v>2</v>
-      </c>
-      <c r="U20" s="18">
+      <c r="S20" s="16">
+        <v>1</v>
+      </c>
+      <c r="T20" s="16">
+        <v>2</v>
+      </c>
+      <c r="U20" s="17">
         <v>3</v>
       </c>
-      <c r="V20" s="19"/>
+      <c r="V20" s="18"/>
       <c r="W20" s="12"/>
       <c r="X20" s="12"/>
     </row>
     <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="22" t="s">
+      <c r="A21" s="47"/>
+      <c r="B21" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="15">
         <v>13</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="16">
+      <c r="E21" s="15">
         <v>7</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="15">
         <v>9</v>
       </c>
       <c r="G21" s="12"/>
-      <c r="H21" s="16">
-        <v>1</v>
-      </c>
-      <c r="I21" s="16">
+      <c r="H21" s="15">
+        <v>1</v>
+      </c>
+      <c r="I21" s="15">
         <v>3</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K21" s="12"/>
-      <c r="L21" s="16">
-        <v>1</v>
-      </c>
-      <c r="M21" s="16">
+      <c r="L21" s="15">
+        <v>1</v>
+      </c>
+      <c r="M21" s="15">
         <v>3</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="15">
         <v>467</v>
       </c>
-      <c r="O21" s="18">
+      <c r="O21" s="17">
         <v>13</v>
       </c>
-      <c r="P21" s="16">
+      <c r="P21" s="15">
         <v>7</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="Q21" s="15">
         <v>9</v>
       </c>
-      <c r="R21" s="16">
-        <v>2</v>
-      </c>
-      <c r="S21" s="18">
-        <v>2</v>
-      </c>
-      <c r="T21" s="18">
+      <c r="R21" s="15">
+        <v>2</v>
+      </c>
+      <c r="S21" s="17">
+        <v>2</v>
+      </c>
+      <c r="T21" s="17">
         <v>3</v>
       </c>
-      <c r="U21" s="18">
+      <c r="U21" s="17">
         <v>6</v>
       </c>
-      <c r="V21" s="19"/>
+      <c r="V21" s="18"/>
       <c r="W21" s="12"/>
       <c r="X21" s="12"/>
     </row>
     <row r="22" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27"/>
-      <c r="B22" s="22" t="s">
+      <c r="A22" s="48"/>
+      <c r="B22" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C22" s="12"/>
@@ -3612,22 +3676,28 @@
       <c r="K22" s="12"/>
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
-      <c r="N22" s="16">
-        <v>1</v>
-      </c>
-      <c r="O22" s="20"/>
+      <c r="N22" s="15">
+        <v>1</v>
+      </c>
+      <c r="O22" s="19"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
       <c r="R22" s="12"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="20"/>
-      <c r="U22" s="20"/>
-      <c r="V22" s="20"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="19"/>
+      <c r="U22" s="19"/>
+      <c r="V22" s="19"/>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A15:A22"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="K14:X14"/>
+    <mergeCell ref="A6:A13"/>
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="R1:X1"/>
     <mergeCell ref="C2:F2"/>
@@ -3635,13 +3705,8 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="A15:A22"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="K14:X14"/>
-    <mergeCell ref="A6:A13"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250414.xlsx
+++ b/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250414.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional\04_Git\AI_Power_Studio\20250426_Vipers\01_source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74649DCE-EC4F-4F4D-B8BA-885B952F1E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A149E7F-A227-4AC1-BC34-248B21C444A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4670" yWindow="430" windowWidth="31320" windowHeight="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="41">
   <si>
     <r>
       <rPr>
@@ -425,6 +425,10 @@
   </si>
   <si>
     <t>AC2</t>
+  </si>
+  <si>
+    <t>Balance to Go</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -795,6 +799,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -866,27 +891,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1256,58 +1260,58 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="33"/>
+      <c r="C1" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="40"/>
     </row>
     <row r="2" spans="1:24" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4">
         <v>45761</v>
       </c>
-      <c r="C2" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="41" t="s">
+      <c r="H2" s="45"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="42"/>
+      <c r="L2" s="49"/>
       <c r="M2" s="5"/>
-      <c r="N2" s="43" t="s">
+      <c r="N2" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="45"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="52"/>
       <c r="R2" s="6" t="s">
         <v>6</v>
       </c>
@@ -1366,7 +1370,7 @@
         <v>19</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="O3" s="9" t="s">
         <v>22</v>
@@ -1464,32 +1468,32 @@
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="25"/>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="54"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="31"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="55" t="s">
+      <c r="K5" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="56"/>
-      <c r="T5" s="56"/>
-      <c r="U5" s="56"/>
-      <c r="V5" s="56"/>
-      <c r="W5" s="56"/>
-      <c r="X5" s="57"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="34"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22"/>
@@ -1959,35 +1963,35 @@
     </row>
     <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="12"/>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="54"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="31"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="55" t="s">
+      <c r="K14" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="L14" s="56"/>
-      <c r="M14" s="56"/>
-      <c r="N14" s="56"/>
-      <c r="O14" s="56"/>
-      <c r="P14" s="56"/>
-      <c r="Q14" s="56"/>
-      <c r="R14" s="56"/>
-      <c r="S14" s="56"/>
-      <c r="T14" s="56"/>
-      <c r="U14" s="56"/>
-      <c r="V14" s="56"/>
-      <c r="W14" s="56"/>
-      <c r="X14" s="57"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="33"/>
+      <c r="S14" s="33"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="33"/>
+      <c r="V14" s="33"/>
+      <c r="W14" s="33"/>
+      <c r="X14" s="34"/>
     </row>
     <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="28" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="11">
@@ -2052,7 +2056,7 @@
       <c r="X15" s="12"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="28" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="21" t="s">
@@ -2116,7 +2120,7 @@
       <c r="X16" s="12"/>
     </row>
     <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="28" t="s">
         <v>36</v>
       </c>
       <c r="B17" s="21" t="s">
@@ -2182,7 +2186,7 @@
       <c r="X17" s="12"/>
     </row>
     <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="58" t="s">
+      <c r="A18" s="28" t="s">
         <v>36</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -2246,7 +2250,7 @@
       <c r="X18" s="12"/>
     </row>
     <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58" t="s">
+      <c r="A19" s="28" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="21" t="s">
@@ -2306,7 +2310,7 @@
       <c r="X19" s="12"/>
     </row>
     <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="58" t="s">
+      <c r="A20" s="28" t="s">
         <v>36</v>
       </c>
       <c r="B20" s="21" t="s">
@@ -2366,7 +2370,7 @@
       <c r="X20" s="12"/>
     </row>
     <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="58" t="s">
+      <c r="A21" s="28" t="s">
         <v>36</v>
       </c>
       <c r="B21" s="21" t="s">
@@ -2428,7 +2432,7 @@
       <c r="X21" s="12"/>
     </row>
     <row r="22" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="58" t="s">
+      <c r="A22" s="28" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="21" t="s">
@@ -2508,58 +2512,58 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="33"/>
+      <c r="C1" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="40"/>
     </row>
     <row r="2" spans="1:24" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4">
         <v>45761</v>
       </c>
-      <c r="C2" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="41" t="s">
+      <c r="H2" s="45"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="42"/>
+      <c r="L2" s="49"/>
       <c r="M2" s="5"/>
-      <c r="N2" s="43" t="s">
+      <c r="N2" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="45"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="52"/>
       <c r="R2" s="6" t="s">
         <v>6</v>
       </c>
@@ -2716,35 +2720,35 @@
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12"/>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="54"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="31"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="55" t="s">
+      <c r="K5" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="56"/>
-      <c r="T5" s="56"/>
-      <c r="U5" s="56"/>
-      <c r="V5" s="56"/>
-      <c r="W5" s="56"/>
-      <c r="X5" s="57"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="34"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="56" t="s">
         <v>37</v>
       </c>
       <c r="B6" s="20" t="s">
@@ -2810,7 +2814,7 @@
       <c r="X6" s="12"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="50"/>
+      <c r="A7" s="57"/>
       <c r="B7" s="21" t="s">
         <v>27</v>
       </c>
@@ -2870,7 +2874,7 @@
       <c r="X7" s="12"/>
     </row>
     <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="50"/>
+      <c r="A8" s="57"/>
       <c r="B8" s="21" t="s">
         <v>28</v>
       </c>
@@ -2932,7 +2936,7 @@
       <c r="X8" s="12"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="50"/>
+      <c r="A9" s="57"/>
       <c r="B9" s="21" t="s">
         <v>29</v>
       </c>
@@ -2992,7 +2996,7 @@
       <c r="X9" s="12"/>
     </row>
     <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="50"/>
+      <c r="A10" s="57"/>
       <c r="B10" s="21" t="s">
         <v>30</v>
       </c>
@@ -3042,7 +3046,7 @@
       <c r="X10" s="12"/>
     </row>
     <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="50"/>
+      <c r="A11" s="57"/>
       <c r="B11" s="21" t="s">
         <v>31</v>
       </c>
@@ -3104,7 +3108,7 @@
       <c r="X11" s="12"/>
     </row>
     <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="50"/>
+      <c r="A12" s="57"/>
       <c r="B12" s="21" t="s">
         <v>32</v>
       </c>
@@ -3166,7 +3170,7 @@
       <c r="X12" s="12"/>
     </row>
     <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="51"/>
+      <c r="A13" s="58"/>
       <c r="B13" s="21" t="s">
         <v>33</v>
       </c>
@@ -3199,35 +3203,35 @@
     </row>
     <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="12"/>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="54"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="31"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="55" t="s">
+      <c r="K14" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="L14" s="56"/>
-      <c r="M14" s="56"/>
-      <c r="N14" s="56"/>
-      <c r="O14" s="56"/>
-      <c r="P14" s="56"/>
-      <c r="Q14" s="56"/>
-      <c r="R14" s="56"/>
-      <c r="S14" s="56"/>
-      <c r="T14" s="56"/>
-      <c r="U14" s="56"/>
-      <c r="V14" s="56"/>
-      <c r="W14" s="56"/>
-      <c r="X14" s="57"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="33"/>
+      <c r="S14" s="33"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="33"/>
+      <c r="V14" s="33"/>
+      <c r="W14" s="33"/>
+      <c r="X14" s="34"/>
     </row>
     <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="53" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="23" t="s">
@@ -3295,7 +3299,7 @@
       <c r="X15" s="12"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="21" t="s">
         <v>27</v>
       </c>
@@ -3357,7 +3361,7 @@
       <c r="X16" s="12"/>
     </row>
     <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="47"/>
+      <c r="A17" s="54"/>
       <c r="B17" s="21" t="s">
         <v>28</v>
       </c>
@@ -3421,7 +3425,7 @@
       <c r="X17" s="12"/>
     </row>
     <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="47"/>
+      <c r="A18" s="54"/>
       <c r="B18" s="21" t="s">
         <v>29</v>
       </c>
@@ -3483,7 +3487,7 @@
       <c r="X18" s="12"/>
     </row>
     <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="21" t="s">
         <v>30</v>
       </c>
@@ -3541,7 +3545,7 @@
       <c r="X19" s="12"/>
     </row>
     <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="47"/>
+      <c r="A20" s="54"/>
       <c r="B20" s="21" t="s">
         <v>31</v>
       </c>
@@ -3599,7 +3603,7 @@
       <c r="X20" s="12"/>
     </row>
     <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="47"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="21" t="s">
         <v>32</v>
       </c>
@@ -3659,7 +3663,7 @@
       <c r="X21" s="12"/>
     </row>
     <row r="22" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="48"/>
+      <c r="A22" s="55"/>
       <c r="B22" s="21" t="s">
         <v>33</v>
       </c>
@@ -3692,12 +3696,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A15:A22"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="K14:X14"/>
-    <mergeCell ref="A6:A13"/>
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="R1:X1"/>
     <mergeCell ref="C2:F2"/>
@@ -3705,6 +3703,12 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="A15:A22"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="K14:X14"/>
+    <mergeCell ref="A6:A13"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250414.xlsx
+++ b/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250414.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional\04_Git\AI_Power_Studio\20250426_Vipers\01_source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\AI_Power_Studio\20250426_Vipers\01_source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A149E7F-A227-4AC1-BC34-248B21C444A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5205813-8782-4A0A-A95C-798C66E3B33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="700" yWindow="4220" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -914,9 +914,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -954,9 +954,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -989,26 +989,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1041,26 +1024,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3696,6 +3662,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A15:A22"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="K14:X14"/>
+    <mergeCell ref="A6:A13"/>
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="R1:X1"/>
     <mergeCell ref="C2:F2"/>
@@ -3703,12 +3675,6 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="A15:A22"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="K14:X14"/>
-    <mergeCell ref="A6:A13"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
